--- a/uploads/20260507_2.xlsx
+++ b/uploads/20260507_2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>JRXKZH</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>JGBM</t>
+  </si>
+  <si>
+    <t>SJRQ</t>
   </si>
   <si>
     <t>DKBH</t>
@@ -1028,13 +1031,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
-    <col min="3" max="3" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="4" width="16.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1062,89 +1065,101 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
         <v>12</v>
+      </c>
+      <c r="D2">
+        <v>20260208</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
         <v>8000000</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
         <v>18</v>
+      </c>
+      <c r="D3">
+        <v>20260208</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
         <v>5000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
       </c>
       <c r="I3" t="s">
         <v>21</v>
       </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
         <v>18</v>
+      </c>
+      <c r="D4">
+        <v>20260208</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
         <v>200</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
-        <v>22</v>
+      <c r="J4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
